--- a/セリフ編集/その他セリフ/11-選択イベント・大型イベント.xlsx
+++ b/セリフ編集/その他セリフ/11-選択イベント・大型イベント.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal._default[1]</t>
+          <t xml:space="preserve">bonus._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal._default[2]</t>
+          <t xml:space="preserve">bonus._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal._default[3]</t>
+          <t xml:space="preserve">bonus._default.normal[3]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="5">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal._default[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal._default[4]</t>
+          <t xml:space="preserve">bonus._default.normal[4]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="5">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal._default[5]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.normal[5]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal._default[5]</t>
+          <t xml:space="preserve">bonus._default.normal[5]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="5">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.bold[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold._default[1]</t>
+          <t xml:space="preserve">bonus._default.bold[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="6">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.bold[2]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold._default[2]</t>
+          <t xml:space="preserve">bonus._default.bold[2]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="6">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.quiet[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.quiet._default[1]</t>
+          <t xml:space="preserve">bonus._default.quiet[1]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="7">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.shy[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.shy._default[1]</t>
+          <t xml:space="preserve">bonus._default.shy[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="8">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing._default[1]</t>
+          <t xml:space="preserve">bonus._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="9">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing._default[2]</t>
+          <t xml:space="preserve">bonus._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="9">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.earnest[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest._default[1]</t>
+          <t xml:space="preserve">bonus._default.earnest[1]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="10">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.earnest[2]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest._default[2]</t>
+          <t xml:space="preserve">bonus._default.earnest[2]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="10">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.emotional[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.emotional._default[1]</t>
+          <t xml:space="preserve">bonus._default.emotional[1]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="10">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.emotional._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus._default.emotional[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.emotional._default[2]</t>
+          <t xml:space="preserve">bonus._default.emotional[2]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="10">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.normal[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.normal._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.normal[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="5">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.normal[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.normal._default[2]</t>
+          <t xml:space="preserve">bonus_repeat._default.normal[2]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="5">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.normal[3]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.normal._default[3]</t>
+          <t xml:space="preserve">bonus_repeat._default.normal[3]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="5">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.bold._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.bold[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="6">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.shy[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.shy._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.shy[1]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="8">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.easygoing._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="9">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.earnest[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.earnest._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.earnest[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="10">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat._default.emotional[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.emotional._default[1]</t>
+          <t xml:space="preserve">bonus_repeat._default.emotional[1]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="10">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.normal[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="5">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal._default[2]</t>
+          <t xml:space="preserve">bonus_insult._default.normal[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="5">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.bold[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.bold._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.bold[1]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="6">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.bold[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.bold._default[2]</t>
+          <t xml:space="preserve">bonus_insult._default.bold[2]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="6">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.quiet._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.quiet[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="7">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.easygoing._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="9">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.earnest[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.earnest._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.earnest[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="10">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult._default.emotional[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.emotional._default[1]</t>
+          <t xml:space="preserve">bonus_insult._default.emotional[1]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.normal[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal._default[1]</t>
+          <t xml:space="preserve">trainer._default.normal[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="5">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.normal[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal._default[2]</t>
+          <t xml:space="preserve">trainer._default.normal[2]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.normal[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal._default[3]</t>
+          <t xml:space="preserve">trainer._default.normal[3]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold._default[1]</t>
+          <t xml:space="preserve">trainer._default.bold[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="6">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.bold[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold._default[2]</t>
+          <t xml:space="preserve">trainer._default.bold[2]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="6">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.quiet._default[1]</t>
+          <t xml:space="preserve">trainer._default.quiet[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="7">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.shy[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.shy._default[1]</t>
+          <t xml:space="preserve">trainer._default.shy[1]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="8">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.easygoing._default[1]</t>
+          <t xml:space="preserve">trainer._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="9">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.earnest[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest._default[1]</t>
+          <t xml:space="preserve">trainer._default.earnest[1]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="10">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.earnest[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest._default[2]</t>
+          <t xml:space="preserve">trainer._default.earnest[2]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer._default.emotional[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.emotional._default[1]</t>
+          <t xml:space="preserve">trainer._default.emotional[1]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="10">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.normal[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal._default[1]</t>
+          <t xml:space="preserve">media._default.normal[1]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="5">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.normal[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal._default[2]</t>
+          <t xml:space="preserve">media._default.normal[2]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="5">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.normal[3]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal._default[3]</t>
+          <t xml:space="preserve">media._default.normal[3]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="5">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.bold[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold._default[1]</t>
+          <t xml:space="preserve">media._default.bold[1]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="6">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.bold[2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold._default[2]</t>
+          <t xml:space="preserve">media._default.bold[2]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="6">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.quiet[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.quiet._default[1]</t>
+          <t xml:space="preserve">media._default.quiet[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="7">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.shy[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.shy._default[1]</t>
+          <t xml:space="preserve">media._default.shy[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="8">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.easygoing._default[1]</t>
+          <t xml:space="preserve">media._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="9">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest._default[1]</t>
+          <t xml:space="preserve">media._default.earnest[1]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.earnest[2]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest._default[2]</t>
+          <t xml:space="preserve">media._default.earnest[2]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="10">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media._default.emotional[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.emotional._default[1]</t>
+          <t xml:space="preserve">media._default.emotional[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="10">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal._default[1]</t>
+          <t xml:space="preserve">encourage._default.normal[1]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="5">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.normal[2]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal._default[2]</t>
+          <t xml:space="preserve">encourage._default.normal[2]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="5">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.normal[3]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal._default[3]</t>
+          <t xml:space="preserve">encourage._default.normal[3]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="5">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold._default[1]</t>
+          <t xml:space="preserve">encourage._default.bold[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="6">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.bold[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold._default[2]</t>
+          <t xml:space="preserve">encourage._default.bold[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="6">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.quiet[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.quiet._default[1]</t>
+          <t xml:space="preserve">encourage._default.quiet[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="7">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.shy[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.shy._default[1]</t>
+          <t xml:space="preserve">encourage._default.shy[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="8">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing._default[1]</t>
+          <t xml:space="preserve">encourage._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="9">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing._default[2]</t>
+          <t xml:space="preserve">encourage._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="9">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.earnest[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest._default[1]</t>
+          <t xml:space="preserve">encourage._default.earnest[1]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.earnest[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest._default[2]</t>
+          <t xml:space="preserve">encourage._default.earnest[2]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2304,7 +2304,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage._default.emotional[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.emotional._default[1]</t>
+          <t xml:space="preserve">encourage._default.emotional[1]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="10">
@@ -2336,7 +2336,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.normal[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.normal[1]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="5">
@@ -2368,7 +2368,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.normal[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal._default[2]</t>
+          <t xml:space="preserve">encourage_high_trust._default.normal[2]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="5">
@@ -2400,7 +2400,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.bold[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.bold[1]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="6">
@@ -2432,7 +2432,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.bold[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold._default[2]</t>
+          <t xml:space="preserve">encourage_high_trust._default.bold[2]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="6">
@@ -2464,7 +2464,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.quiet[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.quiet._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.quiet[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="7">
@@ -2496,7 +2496,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.shy[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.shy._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.shy[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="8">
@@ -2528,7 +2528,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.easygoing._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="9">
@@ -2560,7 +2560,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.earnest[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.earnest[1]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="10">
@@ -2592,7 +2592,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.earnest[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest._default[2]</t>
+          <t xml:space="preserve">encourage_high_trust._default.earnest[2]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="10">
@@ -2624,7 +2624,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust._default.emotional[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.emotional._default[1]</t>
+          <t xml:space="preserve">encourage_high_trust._default.emotional[1]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="10">
@@ -2656,7 +2656,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.normal[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.normal[1]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="5">
@@ -2688,7 +2688,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.normal[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal._default[2]</t>
+          <t xml:space="preserve">refresh_leave._default.normal[2]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="5">
@@ -2720,7 +2720,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.normal[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal._default[3]</t>
+          <t xml:space="preserve">refresh_leave._default.normal[3]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="5">
@@ -2752,7 +2752,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.bold[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.bold[1]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="6">
@@ -2784,7 +2784,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.bold[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold._default[2]</t>
+          <t xml:space="preserve">refresh_leave._default.bold[2]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="6">
@@ -2816,7 +2816,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.quiet[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.quiet._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.quiet[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="7">
@@ -2848,7 +2848,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.shy[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.shy._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.shy[1]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="8">
@@ -2880,7 +2880,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.easygoing._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="9">
@@ -2912,7 +2912,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.earnest[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.earnest[1]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">
@@ -2944,7 +2944,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.earnest[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest._default[2]</t>
+          <t xml:space="preserve">refresh_leave._default.earnest[2]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="10">
@@ -2976,7 +2976,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave._default.emotional[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.emotional._default[1]</t>
+          <t xml:space="preserve">refresh_leave._default.emotional[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="10">
@@ -3008,7 +3008,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.normal[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.normal[1]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="5">
@@ -3040,7 +3040,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.normal[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal._default[2]</t>
+          <t xml:space="preserve">special_treatment._default.normal[2]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="5">
@@ -3072,7 +3072,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.bold[1]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="6">
@@ -3104,7 +3104,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.bold[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold._default[2]</t>
+          <t xml:space="preserve">special_treatment._default.bold[2]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="6">
@@ -3136,7 +3136,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.quiet[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.quiet._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.quiet[1]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="7">
@@ -3168,7 +3168,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.shy[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.shy._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.shy[1]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="8">
@@ -3200,7 +3200,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.easygoing._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="9">
@@ -3232,7 +3232,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.earnest[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.earnest[1]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="10">
@@ -3264,7 +3264,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.earnest[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest._default[2]</t>
+          <t xml:space="preserve">special_treatment._default.earnest[2]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="10">
@@ -3296,7 +3296,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment._default.emotional[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.emotional._default[1]</t>
+          <t xml:space="preserve">special_treatment._default.emotional[1]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="10">
@@ -3328,7 +3328,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal._default[1]</t>
+          <t xml:space="preserve">party._default.normal[1]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="5">
@@ -3360,7 +3360,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.normal[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal._default[2]</t>
+          <t xml:space="preserve">party._default.normal[2]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="5">
@@ -3392,7 +3392,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.normal[3]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal._default[3]</t>
+          <t xml:space="preserve">party._default.normal[3]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="5">
@@ -3424,7 +3424,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal._default[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.normal[4]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal._default[4]</t>
+          <t xml:space="preserve">party._default.normal[4]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="5">
@@ -3456,7 +3456,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold._default[1]</t>
+          <t xml:space="preserve">party._default.bold[1]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="6">
@@ -3488,7 +3488,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.bold[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold._default[2]</t>
+          <t xml:space="preserve">party._default.bold[2]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="6">
@@ -3520,7 +3520,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.quiet[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.quiet._default[1]</t>
+          <t xml:space="preserve">party._default.quiet[1]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="7">
@@ -3552,7 +3552,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.shy[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.shy._default[1]</t>
+          <t xml:space="preserve">party._default.shy[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="8">
@@ -3584,7 +3584,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing._default[1]</t>
+          <t xml:space="preserve">party._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="9">
@@ -3616,7 +3616,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing._default[2]</t>
+          <t xml:space="preserve">party._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="9">
@@ -3648,7 +3648,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest._default[1]</t>
+          <t xml:space="preserve">party._default.earnest[1]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="10">
@@ -3680,7 +3680,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.earnest[2]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest._default[2]</t>
+          <t xml:space="preserve">party._default.earnest[2]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="10">
@@ -3712,7 +3712,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.emotional[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.emotional._default[1]</t>
+          <t xml:space="preserve">party._default.emotional[1]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="10">
@@ -3744,7 +3744,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.emotional._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party._default.emotional[2]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.emotional._default[2]</t>
+          <t xml:space="preserve">party._default.emotional[2]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="10">
@@ -3776,7 +3776,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal._default[1]</t>
+          <t xml:space="preserve">camp._default.normal[1]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="5">
@@ -3808,7 +3808,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.normal[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal._default[2]</t>
+          <t xml:space="preserve">camp._default.normal[2]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="5">
@@ -3840,7 +3840,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.normal[3]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal._default[3]</t>
+          <t xml:space="preserve">camp._default.normal[3]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="5">
@@ -3872,7 +3872,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal._default[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.normal[4]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal._default[4]</t>
+          <t xml:space="preserve">camp._default.normal[4]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="5">
@@ -3904,7 +3904,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold._default[1]</t>
+          <t xml:space="preserve">camp._default.bold[1]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="6">
@@ -3936,7 +3936,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.bold[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold._default[2]</t>
+          <t xml:space="preserve">camp._default.bold[2]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="6">
@@ -3968,7 +3968,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.quiet._default[1]</t>
+          <t xml:space="preserve">camp._default.quiet[1]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="7">
@@ -4000,7 +4000,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.shy[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.shy._default[1]</t>
+          <t xml:space="preserve">camp._default.shy[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="8">
@@ -4032,7 +4032,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing._default[1]</t>
+          <t xml:space="preserve">camp._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="9">
@@ -4064,7 +4064,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing._default[2]</t>
+          <t xml:space="preserve">camp._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="9">
@@ -4096,7 +4096,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest._default[1]</t>
+          <t xml:space="preserve">camp._default.earnest[1]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="10">
@@ -4128,7 +4128,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.earnest[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest._default[2]</t>
+          <t xml:space="preserve">camp._default.earnest[2]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="10">
@@ -4160,7 +4160,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest._default[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.earnest[3]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest._default[3]</t>
+          <t xml:space="preserve">camp._default.earnest[3]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="10">
@@ -4192,7 +4192,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp._default.emotional[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.emotional._default[1]</t>
+          <t xml:space="preserve">camp._default.emotional[1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="10">
@@ -4305,7 +4305,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4320,24 +4320,24 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.composed[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">faction_decree._default.bold[1]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。決めたのなら、それでいいよ</t>
+          <t xml:space="preserve">あれは徒党じゃない。私が呼んで、集まってくれた仲間です</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.composed[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.bold[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4352,24 +4352,24 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.composed[2]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">faction_decree._default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、いつかこうなる気はしてた。従うよ</t>
+          <t xml:space="preserve">納得はしていません。それでも、従います</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.emotional[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4384,24 +4384,24 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">faction_decree._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。異は申しません</t>
+          <t xml:space="preserve">どうして…！ わたし、何か間違えましたか…！</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.ojousama[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.emotional[2]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">faction_decree._default.emotional[2]</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの一存で始めたこと。畳むのも同じでしょう</t>
+          <t xml:space="preserve">みんな、わたしを信じてついてきてくれたのに…</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4448,24 +4448,24 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.polite[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">faction_decree._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。皆には、わたしから伝えます</t>
+          <t xml:space="preserve">……そう、ですか</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.quiet[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4480,24 +4480,24 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">faction_decree._default.quiet[2]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅん。ずいぶん急なお話ね</t>
+          <t xml:space="preserve">……はい。わかりました</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.seductive[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4512,24 +4512,24 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.seductive[2]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">faction_decree._default.earnest[1]</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら。目障りだったのかしら</t>
+          <t xml:space="preserve">わたしのやり方が、間違っていたということでしょうか</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.earnest[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4544,24 +4544,24 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">faction_decree._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はぁ？ なんだよ、それ</t>
+          <t xml:space="preserve">……もっと、うまくやれたはずでした</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.delinquent[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4576,24 +4576,24 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">faction_decree._default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ……好きにしろよ</t>
+          <t xml:space="preserve">……まあ、決まったなら仕方ないですね</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4608,24 +4608,24 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.cool[1]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">faction_decree._default.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">あーあ。楽しかったんですけどね</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.cool[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.shy[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4640,24 +4640,24 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree._default.cool[2]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">faction_decree._default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……理由くらい、聞きたかった</t>
+          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree._default.shy[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">faction_decree._default.shy[2]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれは徒党じゃない。私が呼んで、集まってくれた仲間です</t>
+          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed._default[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4704,24 +4704,24 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">faction_decree.composed._default[1]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">納得はしていません。それでも、従います</t>
+          <t xml:space="preserve">……そう。決めたのなら、それでいいよ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.emotional._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed._default[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4736,24 +4736,24 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">faction_decree.composed._default[2]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…！ わたし、何か間違えましたか…！</t>
+          <t xml:space="preserve">ま、いつかこうなる気はしてた。従うよ</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.emotional._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama._default[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4768,24 +4768,24 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">faction_decree.ojousama._default[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな、わたしを信じてついてきてくれたのに…</t>
+          <t xml:space="preserve">……承知いたしました。異は申しません</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.quiet._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama._default[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4800,24 +4800,24 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">faction_decree.ojousama._default[2]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、ですか</t>
+          <t xml:space="preserve">わたくしの一存で始めたこと。畳むのも同じでしょう</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.quiet._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite._default[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4832,24 +4832,24 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">faction_decree.polite._default[1]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。わかりました</t>
+          <t xml:space="preserve">……はい。皆には、わたしから伝えます</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive._default[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4864,24 +4864,24 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">faction_decree.seductive._default[1]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしのやり方が、間違っていたということでしょうか</t>
+          <t xml:space="preserve">……ふぅん。ずいぶん急なお話ね</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive._default[2]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">faction_decree.seductive._default[2]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もっと、うまくやれたはずでした</t>
+          <t xml:space="preserve">あら。目障りだったのかしら</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent._default[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4928,24 +4928,24 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">faction_decree.delinquent._default[1]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、決まったなら仕方ないですね</t>
+          <t xml:space="preserve">……はぁ？ なんだよ、それ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent._default[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4960,24 +4960,24 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">faction_decree.delinquent._default[2]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あーあ。楽しかったんですけどね</t>
+          <t xml:space="preserve">ちっ……好きにしろよ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.shy._default[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.cool._default[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4992,24 +4992,24 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">faction_decree.cool._default[1]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
+          <t xml:space="preserve">……了解</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.shy._default[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.cool._default[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">faction_decree.cool._default[2]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
+          <t xml:space="preserve">……理由くらい、聞きたかった</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal._default[1]</t>
+          <t xml:space="preserve">S1._default.normal[1]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="5">
@@ -5592,7 +5592,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold._default[1]</t>
+          <t xml:space="preserve">S1._default.bold[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="6">
@@ -5624,7 +5624,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.bold[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold._default[2]</t>
+          <t xml:space="preserve">S1._default.bold[2]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="6">
@@ -5656,7 +5656,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.quiet._default[1]</t>
+          <t xml:space="preserve">S1._default.quiet[1]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="7">
@@ -5688,7 +5688,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.shy[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.shy._default[1]</t>
+          <t xml:space="preserve">S1._default.shy[1]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="8">
@@ -5720,7 +5720,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing._default[1]</t>
+          <t xml:space="preserve">S1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="9">
@@ -5752,7 +5752,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing._default[2]</t>
+          <t xml:space="preserve">S1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="9">
@@ -5784,7 +5784,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest._default[1]</t>
+          <t xml:space="preserve">S1._default.earnest[1]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="10">
@@ -5816,7 +5816,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.earnest[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest._default[2]</t>
+          <t xml:space="preserve">S1._default.earnest[2]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="10">
@@ -5848,7 +5848,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1._default.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.emotional._default[1]</t>
+          <t xml:space="preserve">S1._default.emotional[1]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="10">
@@ -5880,7 +5880,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal._default[1]</t>
+          <t xml:space="preserve">S2._default.normal[1]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="5">
@@ -5912,7 +5912,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold._default[1]</t>
+          <t xml:space="preserve">S2._default.bold[1]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="6">
@@ -5944,7 +5944,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.bold[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold._default[2]</t>
+          <t xml:space="preserve">S2._default.bold[2]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="6">
@@ -5976,7 +5976,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.quiet._default[1]</t>
+          <t xml:space="preserve">S2._default.quiet[1]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="7">
@@ -6008,7 +6008,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.shy._default[1]</t>
+          <t xml:space="preserve">S2._default.shy[1]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="8">
@@ -6040,7 +6040,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing._default[1]</t>
+          <t xml:space="preserve">S2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="9">
@@ -6072,7 +6072,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest._default[1]</t>
+          <t xml:space="preserve">S2._default.earnest[1]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="10">
@@ -6104,7 +6104,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2._default.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.emotional._default[1]</t>
+          <t xml:space="preserve">S2._default.emotional[1]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="10">
@@ -6136,7 +6136,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal._default[1]</t>
+          <t xml:space="preserve">S3._default.normal[1]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="5">
@@ -6168,7 +6168,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold._default[1]</t>
+          <t xml:space="preserve">S3._default.bold[1]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="6">
@@ -6200,7 +6200,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.quiet._default[1]</t>
+          <t xml:space="preserve">S3._default.quiet[1]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="7">
@@ -6232,7 +6232,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.shy[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.shy._default[1]</t>
+          <t xml:space="preserve">S3._default.shy[1]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="8">
@@ -6264,7 +6264,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing._default[1]</t>
+          <t xml:space="preserve">S3._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="9">
@@ -6296,7 +6296,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest._default[1]</t>
+          <t xml:space="preserve">S3._default.earnest[1]</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="10">
@@ -6328,7 +6328,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.earnest[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest._default[2]</t>
+          <t xml:space="preserve">S3._default.earnest[2]</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="10">
@@ -6360,7 +6360,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3._default.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.emotional._default[1]</t>
+          <t xml:space="preserve">S3._default.emotional[1]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="10">
@@ -6392,7 +6392,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.normal[1]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="5">
@@ -6424,7 +6424,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.bold[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="6">
@@ -6456,7 +6456,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.bold[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold._default[2]</t>
+          <t xml:space="preserve">S4_direct._default.bold[2]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="6">
@@ -6488,7 +6488,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.quiet._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.quiet[1]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="7">
@@ -6520,7 +6520,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.shy[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.shy._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.shy[1]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="8">
@@ -6552,7 +6552,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="9">
@@ -6584,7 +6584,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.earnest[1]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="10">
@@ -6616,7 +6616,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.earnest[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest._default[2]</t>
+          <t xml:space="preserve">S4_direct._default.earnest[2]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="10">
@@ -6648,7 +6648,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct._default.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.emotional._default[1]</t>
+          <t xml:space="preserve">S4_direct._default.emotional[1]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="10">
@@ -6680,7 +6680,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.normal[1]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="5">
@@ -6712,7 +6712,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.bold._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.bold[1]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="6">
@@ -6744,7 +6744,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.quiet._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.quiet[1]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="7">
@@ -6776,7 +6776,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.shy._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.shy[1]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="8">
@@ -6808,7 +6808,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.easygoing._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="9">
@@ -6840,7 +6840,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.earnest._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.earnest[1]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="10">
@@ -6872,7 +6872,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent._default.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.emotional._default[1]</t>
+          <t xml:space="preserve">S4_silent._default.emotional[1]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="10">
@@ -6904,7 +6904,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal._default[1]</t>
+          <t xml:space="preserve">S5._default.normal[1]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="5">
@@ -6936,7 +6936,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold._default[1]</t>
+          <t xml:space="preserve">S5._default.bold[1]</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="6">
@@ -6968,7 +6968,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.bold[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold._default[2]</t>
+          <t xml:space="preserve">S5._default.bold[2]</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="6">
@@ -7000,7 +7000,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.quiet._default[1]</t>
+          <t xml:space="preserve">S5._default.quiet[1]</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="7">
@@ -7032,7 +7032,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.shy[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.shy._default[1]</t>
+          <t xml:space="preserve">S5._default.shy[1]</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="8">
@@ -7064,7 +7064,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing._default[1]</t>
+          <t xml:space="preserve">S5._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="9">
@@ -7096,7 +7096,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest._default[1]</t>
+          <t xml:space="preserve">S5._default.earnest[1]</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="10">
@@ -7128,7 +7128,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5._default.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.emotional._default[1]</t>
+          <t xml:space="preserve">S5._default.emotional[1]</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="10">
@@ -7160,7 +7160,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal._default[1]</t>
+          <t xml:space="preserve">S6._default.normal[1]</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="5">
@@ -7192,7 +7192,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold._default[1]</t>
+          <t xml:space="preserve">S6._default.bold[1]</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="6">
@@ -7224,7 +7224,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.quiet._default[1]</t>
+          <t xml:space="preserve">S6._default.quiet[1]</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="7">
@@ -7256,7 +7256,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.shy._default[1]</t>
+          <t xml:space="preserve">S6._default.shy[1]</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="8">
@@ -7288,7 +7288,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing._default[1]</t>
+          <t xml:space="preserve">S6._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="9">
@@ -7320,7 +7320,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest._default[1]</t>
+          <t xml:space="preserve">S6._default.earnest[1]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="10">
@@ -7352,7 +7352,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.earnest[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest._default[2]</t>
+          <t xml:space="preserve">S6._default.earnest[2]</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="10">
@@ -7384,7 +7384,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6._default.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.emotional._default[1]</t>
+          <t xml:space="preserve">S6._default.emotional[1]</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="10">
@@ -7416,7 +7416,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal._default[1]</t>
+          <t xml:space="preserve">E1._default.normal[1]</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="5">
@@ -7448,7 +7448,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.normal[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal._default[2]</t>
+          <t xml:space="preserve">E1._default.normal[2]</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="5">
@@ -7480,7 +7480,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold._default[1]</t>
+          <t xml:space="preserve">E1._default.bold[1]</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="6">
@@ -7512,7 +7512,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.bold[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold._default[2]</t>
+          <t xml:space="preserve">E1._default.bold[2]</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="6">
@@ -7544,7 +7544,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.quiet._default[1]</t>
+          <t xml:space="preserve">E1._default.quiet[1]</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="7">
@@ -7576,7 +7576,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.shy._default[1]</t>
+          <t xml:space="preserve">E1._default.shy[1]</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="8">
@@ -7608,7 +7608,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing._default[1]</t>
+          <t xml:space="preserve">E1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="9">
@@ -7640,7 +7640,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing._default[2]</t>
+          <t xml:space="preserve">E1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="9">
@@ -7672,7 +7672,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest._default[1]</t>
+          <t xml:space="preserve">E1._default.earnest[1]</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="10">
@@ -7704,7 +7704,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1._default.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.emotional._default[1]</t>
+          <t xml:space="preserve">E1._default.emotional[1]</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="10">
@@ -7736,7 +7736,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4._default.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal._default[1]</t>
+          <t xml:space="preserve">E4._default.normal[1]</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="5">
@@ -7768,7 +7768,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal._default[1]</t>
+          <t xml:space="preserve">E6._default.normal[1]</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="5">
@@ -7800,7 +7800,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold._default[1]</t>
+          <t xml:space="preserve">E6._default.bold[1]</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="6">
@@ -7832,7 +7832,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.bold[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold._default[2]</t>
+          <t xml:space="preserve">E6._default.bold[2]</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="6">
@@ -7864,7 +7864,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.quiet._default[1]</t>
+          <t xml:space="preserve">E6._default.quiet[1]</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="7">
@@ -7896,7 +7896,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.shy._default[1]</t>
+          <t xml:space="preserve">E6._default.shy[1]</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="8">
@@ -7928,7 +7928,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing._default[1]</t>
+          <t xml:space="preserve">E6._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="9">
@@ -7960,7 +7960,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest._default[1]</t>
+          <t xml:space="preserve">E6._default.earnest[1]</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="10">
@@ -7992,7 +7992,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.earnest[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest._default[2]</t>
+          <t xml:space="preserve">E6._default.earnest[2]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="10">
@@ -8024,7 +8024,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6._default.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.emotional._default[1]</t>
+          <t xml:space="preserve">E6._default.emotional[1]</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="10">
@@ -8056,7 +8056,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.normal[1]</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="5">
@@ -8088,7 +8088,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.normal[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.normal[2]</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="5">
@@ -8120,7 +8120,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.bold[1]</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="6">
@@ -8152,7 +8152,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.bold[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.bold[2]</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="6">
@@ -8184,7 +8184,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.quiet[1]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="7">
@@ -8216,7 +8216,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.quiet[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.quiet[2]</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="7">
@@ -8248,7 +8248,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="9">
@@ -8280,7 +8280,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="9">
@@ -8312,7 +8312,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.earnest[1]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="10">
@@ -8344,7 +8344,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.earnest[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.earnest[2]</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="10">
@@ -8376,7 +8376,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional._default[1]</t>
+          <t xml:space="preserve">S_boycott._default.emotional[1]</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="10">
@@ -8408,7 +8408,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional._default[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott._default.emotional[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional._default[2]</t>
+          <t xml:space="preserve">S_boycott._default.emotional[2]</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="10">
@@ -8440,7 +8440,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.normal[1]</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="5">
@@ -8472,7 +8472,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.bold._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.bold[1]</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="6">
@@ -8504,7 +8504,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.quiet[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.quiet._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.quiet[1]</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="7">
@@ -8536,7 +8536,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.easygoing._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="9">
@@ -8568,7 +8568,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.earnest._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.earnest[1]</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="10">
@@ -8600,7 +8600,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble._default.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.emotional._default[1]</t>
+          <t xml:space="preserve">S_grumble._default.emotional[1]</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="10">
@@ -8632,7 +8632,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal._default[1]</t>
+          <t xml:space="preserve">S_sns._default.normal[1]</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="5">
@@ -8664,7 +8664,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.bold._default[1]</t>
+          <t xml:space="preserve">S_sns._default.bold[1]</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="6">
@@ -8696,7 +8696,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.quiet._default[1]</t>
+          <t xml:space="preserve">S_sns._default.quiet[1]</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="7">
@@ -8728,7 +8728,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.easygoing._default[1]</t>
+          <t xml:space="preserve">S_sns._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="9">
@@ -8760,7 +8760,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.earnest._default[1]</t>
+          <t xml:space="preserve">S_sns._default.earnest[1]</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="10">
@@ -8792,7 +8792,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns._default.emotional[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.emotional._default[1]</t>
+          <t xml:space="preserve">S_sns._default.emotional[1]</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="10">
@@ -8824,7 +8824,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.normal._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.normal[1]</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="5">
@@ -8856,7 +8856,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.bold._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.bold[1]</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="6">
@@ -8888,7 +8888,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.quiet._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="7">
@@ -8920,7 +8920,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.shy[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.shy._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.shy[1]</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="8">
@@ -8952,7 +8952,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.easygoing._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="9">
@@ -8984,7 +8984,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.earnest._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="10">
@@ -9016,7 +9016,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.emotional._default[1]</t>
+          <t xml:space="preserve">E1.accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="10">
@@ -9048,7 +9048,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.normal._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.normal._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.normal[1]</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="5">
@@ -9080,7 +9080,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.bold._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.bold._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.bold[1]</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="6">
@@ -9112,7 +9112,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.quiet._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.quiet._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.quiet[1]</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="7">
@@ -9144,7 +9144,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.shy._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.shy[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.shy._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.shy[1]</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="8">
@@ -9176,7 +9176,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.easygoing._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.easygoing._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="9">
@@ -9208,7 +9208,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.earnest._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.earnest._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.earnest[1]</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="10">
@@ -9240,7 +9240,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.emotional._default[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend._default.emotional[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.emotional._default[1]</t>
+          <t xml:space="preserve">E1.recommend._default.emotional[1]</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="10">
@@ -9272,7 +9272,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal._default[1]</t>
+          <t xml:space="preserve">B1._default.normal[1]</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="5">
@@ -9304,7 +9304,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.bold[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold._default[1]</t>
+          <t xml:space="preserve">B1._default.bold[1]</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="6">
@@ -9336,7 +9336,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.bold[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold._default[2]</t>
+          <t xml:space="preserve">B1._default.bold[2]</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="6">
@@ -9368,7 +9368,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.quiet._default[1]</t>
+          <t xml:space="preserve">B1._default.quiet[1]</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="7">
@@ -9400,7 +9400,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.shy[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.shy._default[1]</t>
+          <t xml:space="preserve">B1._default.shy[1]</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="8">
@@ -9432,7 +9432,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing._default[1]</t>
+          <t xml:space="preserve">B1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="9">
@@ -9464,7 +9464,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest._default[1]</t>
+          <t xml:space="preserve">B1._default.earnest[1]</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="10">
@@ -9496,7 +9496,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1._default.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.emotional._default[1]</t>
+          <t xml:space="preserve">B1._default.emotional[1]</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="10">
@@ -9528,7 +9528,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.normal[1]</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="5">
@@ -9560,7 +9560,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.bold[1]</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="6">
@@ -9592,7 +9592,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold._default[2]</t>
+          <t xml:space="preserve">B2_fighter1._default.bold[2]</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="6">
@@ -9624,7 +9624,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.quiet._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.quiet[1]</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="7">
@@ -9656,7 +9656,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.shy._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.shy[1]</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="8">
@@ -9688,7 +9688,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="9">
@@ -9720,7 +9720,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.earnest[1]</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="10">
@@ -9752,7 +9752,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.earnest[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest._default[2]</t>
+          <t xml:space="preserve">B2_fighter1._default.earnest[2]</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="10">
@@ -9784,7 +9784,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1._default.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.emotional._default[1]</t>
+          <t xml:space="preserve">B2_fighter1._default.emotional[1]</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="10">
@@ -9816,7 +9816,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.normal[1]</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="5">
@@ -9848,7 +9848,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.bold[1]</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="6">
@@ -9880,7 +9880,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold._default[2]</t>
+          <t xml:space="preserve">B2_fighter2._default.bold[2]</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="6">
@@ -9912,7 +9912,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.quiet[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.quiet._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.quiet[1]</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="7">
@@ -9944,7 +9944,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.shy[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.shy._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.shy[1]</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="8">
@@ -9976,7 +9976,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="9">
@@ -10008,7 +10008,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.earnest[1]</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="10">
@@ -10040,7 +10040,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.earnest[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest._default[2]</t>
+          <t xml:space="preserve">B2_fighter2._default.earnest[2]</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="10">
@@ -10072,7 +10072,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2._default.emotional[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.emotional._default[1]</t>
+          <t xml:space="preserve">B2_fighter2._default.emotional[1]</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="10">
@@ -10104,7 +10104,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.normal[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal._default[1]</t>
+          <t xml:space="preserve">B4._default.normal[1]</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="5">
@@ -10136,7 +10136,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold._default[1]</t>
+          <t xml:space="preserve">B4._default.bold[1]</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="6">
@@ -10168,7 +10168,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.bold[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold._default[2]</t>
+          <t xml:space="preserve">B4._default.bold[2]</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="6">
@@ -10200,7 +10200,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.quiet[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.quiet._default[1]</t>
+          <t xml:space="preserve">B4._default.quiet[1]</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="7">
@@ -10232,7 +10232,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.shy[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.shy._default[1]</t>
+          <t xml:space="preserve">B4._default.shy[1]</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="8">
@@ -10264,7 +10264,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing._default[1]</t>
+          <t xml:space="preserve">B4._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="9">
@@ -10296,7 +10296,7 @@
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing._default[2]</t>
+          <t xml:space="preserve">B4._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="9">
@@ -10328,7 +10328,7 @@
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.earnest[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest._default[1]</t>
+          <t xml:space="preserve">B4._default.earnest[1]</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="10">
@@ -10360,7 +10360,7 @@
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4._default.emotional[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.emotional._default[1]</t>
+          <t xml:space="preserve">B4._default.emotional[1]</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="10">
@@ -10392,7 +10392,7 @@
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.normal[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.normal[1]</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="5">
@@ -10424,7 +10424,7 @@
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.bold[1]</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="6">
@@ -10456,7 +10456,7 @@
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.bold[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold._default[2]</t>
+          <t xml:space="preserve">B4_cm._default.bold[2]</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="6">
@@ -10488,7 +10488,7 @@
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.quiet[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.quiet._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.quiet[1]</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="7">
@@ -10520,7 +10520,7 @@
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.shy[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.shy._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.shy[1]</t>
         </is>
       </c>
       <c r="F324" t="inlineStr" s="8">
@@ -10552,7 +10552,7 @@
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F325" t="inlineStr" s="9">
@@ -10584,7 +10584,7 @@
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_cm._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F326" t="inlineStr" s="9">
@@ -10616,7 +10616,7 @@
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.earnest[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.earnest[1]</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="10">
@@ -10648,7 +10648,7 @@
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm._default.emotional[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.emotional._default[1]</t>
+          <t xml:space="preserve">B4_cm._default.emotional[1]</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="10">
@@ -10680,7 +10680,7 @@
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.normal[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.normal[1]</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="5">
@@ -10712,7 +10712,7 @@
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.bold[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.bold[1]</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="6">
@@ -10744,7 +10744,7 @@
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.bold[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold._default[2]</t>
+          <t xml:space="preserve">B4_gravure._default.bold[2]</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="6">
@@ -10776,7 +10776,7 @@
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.quiet[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.quiet._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.quiet[1]</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="7">
@@ -10808,7 +10808,7 @@
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.shy._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.shy[1]</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="8">
@@ -10840,7 +10840,7 @@
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F334" t="inlineStr" s="9">
@@ -10872,7 +10872,7 @@
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_gravure._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F335" t="inlineStr" s="9">
@@ -10904,7 +10904,7 @@
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.earnest[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.earnest[1]</t>
         </is>
       </c>
       <c r="F336" t="inlineStr" s="10">
@@ -10936,7 +10936,7 @@
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure._default.emotional[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.emotional._default[1]</t>
+          <t xml:space="preserve">B4_gravure._default.emotional[1]</t>
         </is>
       </c>
       <c r="F337" t="inlineStr" s="10">
@@ -10968,7 +10968,7 @@
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.normal[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.normal[1]</t>
         </is>
       </c>
       <c r="F338" t="inlineStr" s="5">
@@ -11000,7 +11000,7 @@
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.bold[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.bold[1]</t>
         </is>
       </c>
       <c r="F339" t="inlineStr" s="6">
@@ -11032,7 +11032,7 @@
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.bold[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold._default[2]</t>
+          <t xml:space="preserve">B4_variety._default.bold[2]</t>
         </is>
       </c>
       <c r="F340" t="inlineStr" s="6">
@@ -11064,7 +11064,7 @@
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.quiet[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.quiet._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.quiet[1]</t>
         </is>
       </c>
       <c r="F341" t="inlineStr" s="7">
@@ -11096,7 +11096,7 @@
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.shy[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.shy._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.shy[1]</t>
         </is>
       </c>
       <c r="F342" t="inlineStr" s="8">
@@ -11128,7 +11128,7 @@
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="9">
@@ -11160,7 +11160,7 @@
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_variety._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="9">
@@ -11192,7 +11192,7 @@
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.earnest[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.earnest[1]</t>
         </is>
       </c>
       <c r="F345" t="inlineStr" s="10">
@@ -11224,7 +11224,7 @@
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety._default.emotional[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.emotional._default[1]</t>
+          <t xml:space="preserve">B4_variety._default.emotional[1]</t>
         </is>
       </c>
       <c r="F346" t="inlineStr" s="10">
@@ -11256,7 +11256,7 @@
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.normal[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.normal[1]</t>
         </is>
       </c>
       <c r="F347" t="inlineStr" s="5">
@@ -11288,7 +11288,7 @@
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.bold[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.bold[1]</t>
         </is>
       </c>
       <c r="F348" t="inlineStr" s="6">
@@ -11320,7 +11320,7 @@
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.bold[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold._default[2]</t>
+          <t xml:space="preserve">B4_brand._default.bold[2]</t>
         </is>
       </c>
       <c r="F349" t="inlineStr" s="6">
@@ -11352,7 +11352,7 @@
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.quiet[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.quiet._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.quiet[1]</t>
         </is>
       </c>
       <c r="F350" t="inlineStr" s="7">
@@ -11384,7 +11384,7 @@
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.shy[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.shy._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.shy[1]</t>
         </is>
       </c>
       <c r="F351" t="inlineStr" s="8">
@@ -11416,7 +11416,7 @@
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F352" t="inlineStr" s="9">
@@ -11448,7 +11448,7 @@
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_brand._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F353" t="inlineStr" s="9">
@@ -11480,7 +11480,7 @@
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.earnest[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.earnest[1]</t>
         </is>
       </c>
       <c r="F354" t="inlineStr" s="10">
@@ -11512,7 +11512,7 @@
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand._default.emotional[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.emotional._default[1]</t>
+          <t xml:space="preserve">B4_brand._default.emotional[1]</t>
         </is>
       </c>
       <c r="F355" t="inlineStr" s="10">
@@ -11544,7 +11544,7 @@
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.normal[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.normal[1]</t>
         </is>
       </c>
       <c r="F356" t="inlineStr" s="5">
@@ -11576,7 +11576,7 @@
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.bold[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.bold[1]</t>
         </is>
       </c>
       <c r="F357" t="inlineStr" s="6">
@@ -11608,7 +11608,7 @@
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.bold[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold._default[2]</t>
+          <t xml:space="preserve">B4_fashion._default.bold[2]</t>
         </is>
       </c>
       <c r="F358" t="inlineStr" s="6">
@@ -11640,7 +11640,7 @@
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.quiet[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.quiet._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.quiet[1]</t>
         </is>
       </c>
       <c r="F359" t="inlineStr" s="7">
@@ -11672,7 +11672,7 @@
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.shy[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.shy._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.shy[1]</t>
         </is>
       </c>
       <c r="F360" t="inlineStr" s="8">
@@ -11704,7 +11704,7 @@
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F361" t="inlineStr" s="9">
@@ -11736,7 +11736,7 @@
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_fashion._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F362" t="inlineStr" s="9">
@@ -11768,7 +11768,7 @@
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.earnest[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.earnest[1]</t>
         </is>
       </c>
       <c r="F363" t="inlineStr" s="10">
@@ -11800,7 +11800,7 @@
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion._default.emotional[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.emotional._default[1]</t>
+          <t xml:space="preserve">B4_fashion._default.emotional[1]</t>
         </is>
       </c>
       <c r="F364" t="inlineStr" s="10">
@@ -11832,7 +11832,7 @@
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.normal[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.normal[1]</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="5">
@@ -11864,7 +11864,7 @@
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.bold[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.bold[1]</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="6">
@@ -11896,7 +11896,7 @@
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.bold[2]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold._default[2]</t>
+          <t xml:space="preserve">B4_fan._default.bold[2]</t>
         </is>
       </c>
       <c r="F367" t="inlineStr" s="6">
@@ -11928,7 +11928,7 @@
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.quiet[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.quiet._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.quiet[1]</t>
         </is>
       </c>
       <c r="F368" t="inlineStr" s="7">
@@ -11960,7 +11960,7 @@
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.shy._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.shy[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.shy._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.shy[1]</t>
         </is>
       </c>
       <c r="F369" t="inlineStr" s="8">
@@ -11992,7 +11992,7 @@
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F370" t="inlineStr" s="9">
@@ -12024,7 +12024,7 @@
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing._default[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing._default[2]</t>
+          <t xml:space="preserve">B4_fan._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F371" t="inlineStr" s="9">
@@ -12056,7 +12056,7 @@
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.earnest[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.earnest[1]</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="10">
@@ -12088,7 +12088,7 @@
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional._default[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan._default.emotional[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.emotional._default[1]</t>
+          <t xml:space="preserve">B4_fan._default.emotional[1]</t>
         </is>
       </c>
       <c r="F373" t="inlineStr" s="10">
